--- a/진로설계4/2026-2/진로설계4 일정.xlsx
+++ b/진로설계4/2026-2/진로설계4 일정.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DESKTOP\Desktop\Teaching\환경경제학\2026-1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DESKTOP\Desktop\00_Teaching\진로설계4\2026-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{135DF230-F8DE-4693-A87A-D9F57E293D11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{116C12E6-FC10-4CE3-86DF-2E5C5453B6D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{3189E96F-9785-4911-B32D-79C365FCCF66}"/>
   </bookViews>
@@ -39,11 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="35">
-  <si>
-    <t>시험</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="31">
   <si>
     <t>비고</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -77,14 +73,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>10월 1일</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10월 8일</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>10월 15일</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -121,63 +109,59 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>경제와 자연환경 (Ch.02), 수요 공급 (Ch.03)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>시장실패(Ch.04)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>환경정책 평가기준 (Ch.05)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>직접규제 (Ch.06)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>배출권거래제 (Ch.08)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>배출부과금과 보조금 (Ch.07)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>불확실성 및 정보비대칭성 (Ch.09)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>환경정책의 정치경제 (Ch.10)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>환경정책 분석 틀. 비용-편익분석 (Ch.13,14)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>전지구 환경문제, 기후변화경제학 (Ch.21,22)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>OT: 환경경제학이란 (Ch.01)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>중간고사</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>기말고사</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>온라인 강의 업로드 (중간고사 전 연습문제 풀이)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>온라인 강의 업로드 (기말고사 전 연습문제 풀이)</t>
+    <t>종강</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지도교수 상담 대체</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>동영상 (A_07)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>동영상 (A_05)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>대면수업</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>선배특강</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>동영상 (A_04)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10월 08일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10월 01일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>청년고용정책 특강</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>추석 (동영상)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>컨설턴트 상담대체</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>직무특강</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -202,7 +186,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -211,13 +195,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.89999084444715716"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF99"/>
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -243,20 +221,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -608,201 +586,197 @@
   <sheetData>
     <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A5" s="5">
+        <v>1</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C5" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="1"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A6" s="5">
+        <v>2</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="1"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A7" s="2">
         <v>3</v>
       </c>
-      <c r="C4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A5" s="1">
-        <v>1</v>
-      </c>
-      <c r="B5" s="1" t="s">
+      <c r="B7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="2"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A8" s="2">
+        <v>4</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="4"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A9" s="2">
         <v>5</v>
       </c>
-      <c r="C5" t="s">
+      <c r="B9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="2"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A10" s="2">
+        <v>6</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D5" s="1"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A6" s="1">
-        <v>2</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="1"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A7" s="1">
-        <v>3</v>
-      </c>
-      <c r="B7" s="1" t="s">
+      <c r="D10" s="2"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A11" s="5">
         <v>7</v>
       </c>
-      <c r="C7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" s="1"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A8" s="4">
-        <v>4</v>
-      </c>
-      <c r="B8" s="4" t="s">
+      <c r="B11" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D8" s="6"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A9" s="1">
-        <v>5</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="C11" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="1"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A10" s="1">
-        <v>6</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" t="s">
-        <v>23</v>
-      </c>
-      <c r="D10" s="1"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A11" s="1">
-        <v>7</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" t="s">
-        <v>25</v>
-      </c>
-      <c r="D11" s="1"/>
+      <c r="D11" s="2"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A12" s="2">
         <v>8</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" s="2"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A13" s="2">
+        <v>9</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" s="2"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A14" s="2">
+        <v>10</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" s="2"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A15" s="5">
+        <v>11</v>
+      </c>
+      <c r="B15" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A13" s="1">
-        <v>9</v>
-      </c>
-      <c r="B13" s="1" t="s">
+      <c r="C15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" s="2"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A16" s="2">
+        <v>12</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C13" t="s">
-        <v>24</v>
-      </c>
-      <c r="D13" s="1"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A14" s="1">
-        <v>10</v>
-      </c>
-      <c r="B14" s="1" t="s">
+      <c r="C16" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16" s="4"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A17" s="2">
+        <v>13</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C14" t="s">
-        <v>26</v>
-      </c>
-      <c r="D14" s="1"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A15" s="1">
-        <v>11</v>
-      </c>
-      <c r="B15" s="1" t="s">
+      <c r="C17" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" s="2"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A18" s="2">
+        <v>14</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C15" t="s">
-        <v>27</v>
-      </c>
-      <c r="D15" s="1"/>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A16" s="4">
-        <v>12</v>
-      </c>
-      <c r="B16" s="4" t="s">
+      <c r="C18" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D18" s="2"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A19" s="5">
+        <v>15</v>
+      </c>
+      <c r="B19" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D16" s="6"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A17" s="1">
-        <v>13</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C17" t="s">
-        <v>28</v>
-      </c>
-      <c r="D17" s="1"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A18" s="1">
-        <v>14</v>
-      </c>
-      <c r="B18" s="1" t="s">
+      <c r="C19" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C18" t="s">
-        <v>29</v>
-      </c>
-      <c r="D18" s="1"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A19" s="2">
-        <v>15</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>0</v>
-      </c>
+      <c r="D19" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
